--- a/Mappe1.xlsx
+++ b/Mappe1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\station\Documents\Code\Physik_helfer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5B3C6D-CEBC-427B-A56D-86202B393364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EA783C-6E9D-4A75-A7CB-20855DF05A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4BDF549-2D7C-4ED6-BBDE-4230E0A14C34}"/>
   </bookViews>
@@ -16,13 +16,16 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_PLVS_ULTRA_Analysis" hidden="1">"Datenbereich: Tabelle1: D1:E8 — Diagramm erstellen."</definedName>
+    <definedName name="_PLVS_ULTRA_Analysis" hidden="1">"Unabhängig: Strecke [m]; Abhängig: Zeit [s] | Zusammenhang: Strecke in m → Zeit in s | Diagramm: Säulendiagramm; Trendli"&amp;"nie: gleitender Durchschnitt (Periode 2) | Messpunkte: 7 von 7; Mittelwert y: 4 s | Statistik: Median y: 4 s; Min–Max y:"&amp;" 1–7 s; Stdabw. y: 2.16 s; Korrelation: 0.9774 | KI-Einschätzung: 100% — Strecke ist quadratisch abhängig von Zeit (Stre"&amp;"cke = Zeit²), perfekte quadratische Korrelation (R²=1.0)."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_1" hidden="1">"Unabhängig: Zeit in s; Abhängig: Strecke in m | Zusammenhang: Zeit in s → Strecke in m | Diagramm: Punkt- und Liniendiag"&amp;"ramm; Trendlinie: quadratisch | Messpunkte: 7 von 7; Mittelwert y: 20 m | Statistik: Median y: 16 m; Min–Max y: 1–49 m; "&amp;"Stdabw. y: 17.68 m; Korrelation: 0.9774 | KI-Einschätzung: 95% — Die Strecke folgt einem quadratischen Muster (≈ Zeit²),"&amp;" was auf einen quadratischen Zusammenhang hindeutet."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_2" hidden="1">"Unabhängig: Monat; Abhängig: Aktienpreis | Zusammenhang: Monat → Aktienpreis | Diagramm: Punkt- und Liniendiagramm; Tren"&amp;"dlinie: kein | Messpunkte: 6 von 6; Mittelwert y: 135.1 | Statistik: Median y: 145; Min–Max y: 90–170; Stdabw. y: 32.63;"&amp;" Korrelation: 0.4063 | Veränderung: Kurs 100.4 → 160; absolut +59.6; Prozent: +59.36% | KI-Einschätzung: 90% — Monat ist"&amp;" unabhängige Zeitvariable, Aktienpreis abhängige Messgröße. Verlauf stark volatil mit Abfall im 4. Monat, keine Trendfun"&amp;"ktion st..."</definedName>
+    <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_3" hidden="1">"Unabhängig: Strecke [m]; Abhängig: Zeit [s] | Zusammenhang: Strecke in m → Zeit in s | Diagramm: Säulendiagramm; Trendli"&amp;"nie: gleitender Durchschnitt (Periode 2) | Messpunkte: 7 von 7; Mittelwert y: 4 s | Statistik: Median y: 4 s; Min–Max y:"&amp;" 1–7 s; Stdabw. y: 2.16 s; Korrelation: 0.9774 | KI-Einschätzung: 100% — Strecke ist quadratisch abhängig von Zeit (Stre"&amp;"cke = Zeit²), perfekte quadratische Korrelation (R²=1.0)."</definedName>
     <definedName name="_PLVS_ULTRA_ChartSheet" hidden="1">"Tabelle1"</definedName>
-    <definedName name="_PLVS_ULTRA_SourceAddress" hidden="1">"$D$1:$E$8"</definedName>
-    <definedName name="_PLVS_ULTRA_SourceLabel" hidden="1">"Tabelle1: D1:E8"</definedName>
+    <definedName name="_PLVS_ULTRA_LastChart" hidden="1">"PLVS_ULTRA_Chart_3"</definedName>
+    <definedName name="_PLVS_ULTRA_SourceAddress" hidden="1">"$A$1:$B$8"</definedName>
+    <definedName name="_PLVS_ULTRA_SourceLabel" hidden="1">"Tabelle1: A1:B8"</definedName>
     <definedName name="_PLVS_ULTRA_SourceSheet" hidden="1">"Tabelle1"</definedName>
+    <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_3" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$A$1:$B$8"",""spec"":{""x_column"":""Strecke in m"",""y_column"":""Zeit in s"",""x_label"":""Strecke [m"&amp;"]"",""y_label"":""Zeit [s]"",""x_unit"":""m"",""y_unit"":""s"",""chart_type"":""column"",""x_min"":null,""x_max"":null,""y_min"":null,""y_max"":n"&amp;"ull,""origin"":false,""trendline"":""moving_average"",""polynomial_degree"":2,""moving_average_period"":2,""x_error_column"":null,""y"&amp;"_error_column"":null,""independent_variable"":""Strecke in m"",""dependent_variable"":""Zeit in s"",""show_points"":false,""connect_"&amp;"points"":false,""confidence"":1.0,""reason"":""Strecke ist quadratisch abhängig von Zeit (Strecke = Zeit²), perfekte quadratis"&amp;"che Korrelation (R²=1.0).""},""settings"":{""show_points"":false,""connect_points"":false,""legend"":true,""title"":""Zeit [s] in Ab"&amp;"hängigkeit von Strecke [m]"",""line_width"":3.0,""point_size"":5,""series_color"":3243501,""text_formats"":{""title"":{""name"":""Time"&amp;"s New Roman""},""x_axis"":{""name"":""Times New Roman""}},""text_target"":""x_axis""}}"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -138,11 +141,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="de-DE"/>
-              <a:t>Aktienpreis in Abhängigkeit von Monat</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Zeit [s] in Abhängigkeit von Strecke [m]</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -152,8 +159,9 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -161,16 +169,40 @@
           <c:tx>
             <c:v>Messwerte</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-          </c:marker>
-          <c:xVal>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="38100" cap="rnd" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:trendline>
+            <c:name>Gleitender Durchschnitt (2)</c:name>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
             <c:numRef>
-              <c:f>Tabelle1!$H$2:$H$7</c:f>
+              <c:f>Tabelle1!$A$2:$A$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -189,40 +221,45 @@
                 <c:pt idx="5">
                   <c:v>6</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$G$2:$G$7</c:f>
+              <c:f>Tabelle1!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>100.4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>140</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>170</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>150</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>160</c:v>
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>49</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5DC9-4D1E-85E4-3AE11BA226AF}"/>
+              <c16:uniqueId val="{00000000-A389-40EC-A581-A665901E5886}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -234,15 +271,14 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1964066767"/>
-        <c:axId val="1964058127"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1964066767"/>
+        <c:gapWidth val="150"/>
+        <c:axId val="1245026896"/>
+        <c:axId val="1245027376"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1245026896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="6"/>
-          <c:min val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -257,7 +293,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="de-DE"/>
-                  <a:t>Monat</a:t>
+                  <a:t>Zeit [s]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -268,16 +304,19 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1964058127"/>
+        <c:crossAx val="1245027376"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="1964058127"/>
+        <c:axId val="1245027376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="170"/>
-          <c:min val="90"/>
+          <c:max val="51.4"/>
+          <c:min val="-1.4000000000000004"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -289,11 +328,15 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr>
+                    <a:latin typeface="Times New Roman"/>
+                    <a:ea typeface="Times New Roman"/>
+                    <a:cs typeface="Times New Roman"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="de-DE"/>
-                  <a:t>Aktienpreis</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Zeit [s]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -304,228 +347,15 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1964066767"/>
+        <c:crossAx val="1245026896"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="de-DE"/>
-              <a:t>Zeit in s in Abhängigkeit von Masse in kg</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
+    <c:legend>
+      <c:legendPos val="r"/>
       <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Messwerte</c:v>
-          </c:tx>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Tabelle1!$D$2:$D$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>64</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Tabelle1!$E$2:$E$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C0D4-46D3-A514-8DF9AFC6B45A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="2122693135"/>
-        <c:axId val="2122695055"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="2122693135"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="64"/>
-          <c:min val="1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="de-DE"/>
-                  <a:t>Masse in kg</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2122695055"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="2122695055"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="7"/>
-          <c:min val="1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="de-DE"/>
-                  <a:t>Zeit in s</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2122693135"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-    </c:plotArea>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -550,22 +380,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>613719</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>171622</xdr:rowOff>
+      <xdr:colOff>519328</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>145877</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>104003</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>118419</xdr:rowOff>
+      <xdr:colOff>9612</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>92675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="PLVS_ULTRA_Chart_2">
+        <xdr:cNvPr id="2" name="PLVS_ULTRA_Chart_3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E759B8D9-A97F-F3D2-60EC-6678F3FAF7C0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C099EAC4-76C7-C31C-FD0B-68F07250258C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -578,42 +408,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>54919</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>181919</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="PLVS_ULTRA_Chart_3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BECE08F-25A8-0FD5-6BEA-3F2FC29E4BC3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>

--- a/Mappe1.xlsx
+++ b/Mappe1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\station\Documents\Code\Physik_helfer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EA783C-6E9D-4A75-A7CB-20855DF05A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C706E7C-2D9E-4C2C-B7FD-15582863770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4BDF549-2D7C-4ED6-BBDE-4230E0A14C34}"/>
   </bookViews>
@@ -16,16 +16,20 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_PLVS_ULTRA_Analysis" hidden="1">"Unabhängig: Strecke [m]; Abhängig: Zeit [s] | Zusammenhang: Strecke in m → Zeit in s | Diagramm: Säulendiagramm; Trendli"&amp;"nie: gleitender Durchschnitt (Periode 2) | Messpunkte: 7 von 7; Mittelwert y: 4 s | Statistik: Median y: 4 s; Min–Max y:"&amp;" 1–7 s; Stdabw. y: 2.16 s; Korrelation: 0.9774 | KI-Einschätzung: 100% — Strecke ist quadratisch abhängig von Zeit (Stre"&amp;"cke = Zeit²), perfekte quadratische Korrelation (R²=1.0)."</definedName>
+    <definedName name="_PLVS_ULTRA_Analysis" hidden="1">"Unabhängig: Zeit [s]; Abhängig: Masse [kg] | Zusammenhang: Zeit in s → Masse in kg | Diagramm: Säulendiagramm; Trendlini"&amp;"e: exponentiell | Messpunkte: 7 von 7; Mittelwert y: 18.14 kg | Statistik: Median y: 8 kg; Min–Max y: 1–64 kg; Stdabw. y"&amp;": 22.94 kg; Korrelation: 0.8779 | KI-Einschätzung: 95% — Exponential fit (R²=1) shows mass doubling each second, best mo"&amp;"del is exponential."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_1" hidden="1">"Unabhängig: Zeit in s; Abhängig: Strecke in m | Zusammenhang: Zeit in s → Strecke in m | Diagramm: Punkt- und Liniendiag"&amp;"ramm; Trendlinie: quadratisch | Messpunkte: 7 von 7; Mittelwert y: 20 m | Statistik: Median y: 16 m; Min–Max y: 1–49 m; "&amp;"Stdabw. y: 17.68 m; Korrelation: 0.9774 | KI-Einschätzung: 95% — Die Strecke folgt einem quadratischen Muster (≈ Zeit²),"&amp;" was auf einen quadratischen Zusammenhang hindeutet."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_2" hidden="1">"Unabhängig: Monat; Abhängig: Aktienpreis | Zusammenhang: Monat → Aktienpreis | Diagramm: Punkt- und Liniendiagramm; Tren"&amp;"dlinie: kein | Messpunkte: 6 von 6; Mittelwert y: 135.1 | Statistik: Median y: 145; Min–Max y: 90–170; Stdabw. y: 32.63;"&amp;" Korrelation: 0.4063 | Veränderung: Kurs 100.4 → 160; absolut +59.6; Prozent: +59.36% | KI-Einschätzung: 90% — Monat ist"&amp;" unabhängige Zeitvariable, Aktienpreis abhängige Messgröße. Verlauf stark volatil mit Abfall im 4. Monat, keine Trendfun"&amp;"ktion st..."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_3" hidden="1">"Unabhängig: Strecke [m]; Abhängig: Zeit [s] | Zusammenhang: Strecke in m → Zeit in s | Diagramm: Säulendiagramm; Trendli"&amp;"nie: gleitender Durchschnitt (Periode 2) | Messpunkte: 7 von 7; Mittelwert y: 4 s | Statistik: Median y: 4 s; Min–Max y:"&amp;" 1–7 s; Stdabw. y: 2.16 s; Korrelation: 0.9774 | KI-Einschätzung: 100% — Strecke ist quadratisch abhängig von Zeit (Stre"&amp;"cke = Zeit²), perfekte quadratische Korrelation (R²=1.0)."</definedName>
+    <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_4" hidden="1">"Unabhängig: Strecke [m]; Abhängig: Zeit [s] | Zusammenhang: Strecke in m → Zeit in s | Diagramm: Punktdiagramm (XY); Tre"&amp;"ndlinie: polynomisch (Grad 2) | Messpunkte: 7 von 7; Mittelwert y: 4 s | Statistik: Median y: 4 s; Min–Max y: 1–7 s; Std"&amp;"abw. y: 2.16 s; Korrelation: 0.9774 | KI-Einschätzung: 100% — The data represents a perfect quadratic relationship where"&amp;" distance (Strecke in m) is the square of time (Zeit in s), with R² = 1.0 for a..."</definedName>
+    <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_5" hidden="1">"Unabhängig: Zeit [s]; Abhängig: Masse [kg] | Zusammenhang: Zeit in s → Masse in kg | Diagramm: Säulendiagramm; Trendlini"&amp;"e: exponentiell | Messpunkte: 7 von 7; Mittelwert y: 18.14 kg | Statistik: Median y: 8 kg; Min–Max y: 1–64 kg; Stdabw. y"&amp;": 22.94 kg; Korrelation: 0.8779 | KI-Einschätzung: 95% — Exponential fit (R²=1) shows mass doubling each second, best mo"&amp;"del is exponential."</definedName>
     <definedName name="_PLVS_ULTRA_ChartSheet" hidden="1">"Tabelle1"</definedName>
-    <definedName name="_PLVS_ULTRA_LastChart" hidden="1">"PLVS_ULTRA_Chart_3"</definedName>
-    <definedName name="_PLVS_ULTRA_SourceAddress" hidden="1">"$A$1:$B$8"</definedName>
-    <definedName name="_PLVS_ULTRA_SourceLabel" hidden="1">"Tabelle1: A1:B8"</definedName>
+    <definedName name="_PLVS_ULTRA_LastChart" hidden="1">"PLVS_ULTRA_Chart_5"</definedName>
+    <definedName name="_PLVS_ULTRA_SourceAddress" hidden="1">"$D$1:$E$8"</definedName>
+    <definedName name="_PLVS_ULTRA_SourceLabel" hidden="1">"Tabelle1: D1:E8"</definedName>
     <definedName name="_PLVS_ULTRA_SourceSheet" hidden="1">"Tabelle1"</definedName>
-    <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_3" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$A$1:$B$8"",""spec"":{""x_column"":""Strecke in m"",""y_column"":""Zeit in s"",""x_label"":""Strecke [m"&amp;"]"",""y_label"":""Zeit [s]"",""x_unit"":""m"",""y_unit"":""s"",""chart_type"":""column"",""x_min"":null,""x_max"":null,""y_min"":null,""y_max"":n"&amp;"ull,""origin"":false,""trendline"":""moving_average"",""polynomial_degree"":2,""moving_average_period"":2,""x_error_column"":null,""y"&amp;"_error_column"":null,""independent_variable"":""Strecke in m"",""dependent_variable"":""Zeit in s"",""show_points"":false,""connect_"&amp;"points"":false,""confidence"":1.0,""reason"":""Strecke ist quadratisch abhängig von Zeit (Strecke = Zeit²), perfekte quadratis"&amp;"che Korrelation (R²=1.0).""},""settings"":{""show_points"":false,""connect_points"":false,""legend"":true,""title"":""Zeit [s] in Ab"&amp;"hängigkeit von Strecke [m]"",""line_width"":3.0,""point_size"":5,""series_color"":3243501,""text_formats"":{""title"":{""name"":""Time"&amp;"s New Roman""},""x_axis"":{""name"":""Times New Roman""}},""text_target"":""x_axis""}}"</definedName>
+    <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_3" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$A$1:$B$8"",""spec"":{""x_column"":""Strecke in m"",""y_column"":""Zeit in s"",""x_label"":""Strecke [m"&amp;"]"",""y_label"":""Zeit [s]"",""x_unit"":""m"",""y_unit"":""s"",""chart_type"":""column"",""x_min"":null,""x_max"":null,""y_min"":null,""y_max"":n"&amp;"ull,""origin"":false,""trendline"":""moving_average"",""polynomial_degree"":2,""moving_average_period"":2,""x_error_column"":null,""y"&amp;"_error_column"":null,""independent_variable"":""Strecke in m"",""dependent_variable"":""Zeit in s"",""show_points"":false,""connect_"&amp;"points"":false,""confidence"":1.0,""reason"":""Strecke ist quadratisch abhängig von Zeit (Strecke = Zeit²), perfekte quadratis"&amp;"che Korrelation (R²=1.0).""},""settings"":{""show_points"":false,""connect_points"":false,""legend"":true,""title"":""Zeit [s] in Ab"&amp;"hängigkeit von Strecke [m]"",""line_width"":3.0,""point_size"":5,""series_color"":3243501,""text_formats"":{""title"":{""name"":""Time"&amp;"s New Roman""},""x_axis"":{""name"":""Times New Roman"",""size"":20,""italic"":true}},""text_target"":""x_axis""}}"</definedName>
+    <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_4" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$A$1:$B$8"",""spec"":{""x_column"":""Strecke in m"",""y_column"":""Zeit in s"",""x_label"":""Strecke [m"&amp;"]"",""y_label"":""Zeit [s]"",""x_unit"":""m"",""y_unit"":""s"",""chart_type"":""scatter"",""x_min"":null,""x_max"":null,""y_min"":null,""y_max"":"&amp;"null,""origin"":false,""trendline"":""polynomial"",""polynomial_degree"":2,""moving_average_period"":3,""x_error_column"":null,""y_er"&amp;"ror_column"":null,""independent_variable"":""Strecke in m"",""dependent_variable"":""Zeit in s"",""show_points"":true,""connect_poin"&amp;"ts"":false,""confidence"":1.0,""reason"":""The data represents a perfect quadratic relationship where distance (Strecke in m) "&amp;"is the square of time (Zeit in s), with R² = 1.0 for a quadratic fit.""},""settings"":{""show_points"":true,""connect_points"":"&amp;"false,""legend"":false,""title"":""Zeit [s] in Abhängigkeit von Strecke [m]"",""line_width"":3.0,""point_size"":5,""text_formats"":{"&amp;"""title"":{""italic"":true,""size"":12,""name"":""Times New Roman""},""x_axis"":{""italic"":true,""size"":20},""y_axis"":{""italic"":true,""n"&amp;"ame"":""Times New Roman""}},""text_target"":""title"",""series_color"":3243501,""line_color"":8544277,""gridlines_enabled"":true}}"</definedName>
+    <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_5" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$D$1:$E$8"",""spec"":{""x_column"":""Zeit in s"",""y_column"":""Masse in kg"",""x_label"":""Zeit [s]"","""&amp;"y_label"":""Masse [kg]"",""x_unit"":""s"",""y_unit"":""kg"",""chart_type"":""column"",""x_min"":1.0,""x_max"":7.0,""y_min"":1.0,""y_max"":64.0,"&amp;"""origin"":false,""trendline"":""exponential"",""polynomial_degree"":2,""moving_average_period"":3,""x_error_column"":null,""y_error_"&amp;"column"":null,""independent_variable"":""Zeit in s"",""dependent_variable"":""Masse in kg"",""show_points"":false,""connect_points"":"&amp;"false,""confidence"":0.95,""reason"":""Exponential fit (R²=1) shows mass doubling each second, best model is exponential.""},"""&amp;"settings"":{""show_points"":false,""connect_points"":false,""legend"":false,""gridlines_enabled"":true,""title"":""Masse [kg] in Abh"&amp;"ängigkeit von Zeit [s]"",""text_formats"":{""title"":{""name"":""Segoe UI""}},""point_size"":5,""line_color"":16777215,""line_width"":3"&amp;".0,""series_color"":12874308}}"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -142,14 +146,14 @@
           <a:p>
             <a:pPr>
               <a:defRPr>
-                <a:latin typeface="Times New Roman"/>
-                <a:ea typeface="Times New Roman"/>
-                <a:cs typeface="Times New Roman"/>
+                <a:latin typeface="Segoe UI"/>
+                <a:ea typeface="Segoe UI"/>
+                <a:cs typeface="Segoe UI"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Zeit [s] in Abhängigkeit von Strecke [m]</a:t>
+              <a:t>Masse [kg] in Abhängigkeit von Zeit [s]</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -171,17 +175,19 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ED7D31"/>
+              <a:srgbClr val="4472C4"/>
             </a:solidFill>
-            <a:ln w="38100">
+            <a:ln w="38100" cap="rnd" cmpd="sng" algn="ctr">
               <a:noFill/>
+              <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
             <a:extLst>
               <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
                 <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="38100" cap="rnd" cmpd="sng" algn="ctr">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
                   <a:prstDash val="solid"/>
                   <a:round/>
@@ -191,15 +197,14 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:trendline>
-            <c:name>Gleitender Durchschnitt (2)</c:name>
-            <c:trendlineType val="movingAvg"/>
-            <c:period val="2"/>
+            <c:name>Exponential Fit</c:name>
+            <c:trendlineType val="exp"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>Tabelle1!$A$2:$A$8</c:f>
+              <c:f>Tabelle1!$E$2:$E$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -229,7 +234,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$B$2:$B$8</c:f>
+              <c:f>Tabelle1!$D$2:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -237,29 +242,29 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
                 <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>25</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>36</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>49</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A389-40EC-A581-A665901E5886}"/>
+              <c16:uniqueId val="{00000002-4230-4937-A3A2-91154FC9F654}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -272,16 +277,17 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1245026896"/>
-        <c:axId val="1245027376"/>
+        <c:axId val="1231230416"/>
+        <c:axId val="1231236656"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1245026896"/>
+        <c:axId val="1231230416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines/>
         <c:title>
           <c:tx>
             <c:rich>
@@ -290,49 +296,6 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="de-DE"/>
-                  <a:t>Zeit [s]</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1245027376"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1245027376"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="51.4"/>
-          <c:min val="-1.4000000000000004"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr>
-                    <a:latin typeface="Times New Roman"/>
-                    <a:ea typeface="Times New Roman"/>
-                    <a:cs typeface="Times New Roman"/>
-                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
@@ -347,15 +310,49 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1245026896"/>
+        <c:crossAx val="1231236656"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1231236656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="64"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Masse [kg]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1231230416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -380,22 +377,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>519328</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>145877</xdr:rowOff>
+      <xdr:colOff>596557</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>68648</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>9612</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>92675</xdr:rowOff>
+      <xdr:colOff>86841</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>15445</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="PLVS_ULTRA_Chart_3">
+        <xdr:cNvPr id="2" name="PLVS_ULTRA_Chart_5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C099EAC4-76C7-C31C-FD0B-68F07250258C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED8A869-A37E-1784-3D92-6000AA2994E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Mappe1.xlsx
+++ b/Mappe1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\station\Documents\Code\Physik_helfer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C706E7C-2D9E-4C2C-B7FD-15582863770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D142D1CD-DC65-42EF-A931-87C42DF20B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4BDF549-2D7C-4ED6-BBDE-4230E0A14C34}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_PLVS_ULTRA_Analysis" hidden="1">"Unabhängig: Zeit [s]; Abhängig: Masse [kg] | Zusammenhang: Zeit in s → Masse in kg | Diagramm: Säulendiagramm; Trendlini"&amp;"e: exponentiell | Messpunkte: 7 von 7; Mittelwert y: 18.14 kg | Statistik: Median y: 8 kg; Min–Max y: 1–64 kg; Stdabw. y"&amp;": 22.94 kg; Korrelation: 0.8779 | KI-Einschätzung: 95% — Exponential fit (R²=1) shows mass doubling each second, best mo"&amp;"del is exponential."</definedName>
+    <definedName name="_PLVS_ULTRA_Analysis" hidden="1">"Unabhängig: Zeit [s]; Abhängig: Masse [kg] | Zusammenhang: Zeit in s → Masse in kg | Diagramm: Punktdiagramm (XY); Trend"&amp;"linie: exponentiell | Messpunkte: 7 von 7; Mittelwert y: 18.14 kg | Statistik: Median y: 8 kg; Min–Max y: 1–64 kg; Stdab"&amp;"w. y: 22.94 kg; Korrelation: 0.8779 | KI-Einschätzung: 95% — Exponential fit (R²=1) shows mass doubling each second, bes"&amp;"t model is exponential."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_1" hidden="1">"Unabhängig: Zeit in s; Abhängig: Strecke in m | Zusammenhang: Zeit in s → Strecke in m | Diagramm: Punkt- und Liniendiag"&amp;"ramm; Trendlinie: quadratisch | Messpunkte: 7 von 7; Mittelwert y: 20 m | Statistik: Median y: 16 m; Min–Max y: 1–49 m; "&amp;"Stdabw. y: 17.68 m; Korrelation: 0.9774 | KI-Einschätzung: 95% — Die Strecke folgt einem quadratischen Muster (≈ Zeit²),"&amp;" was auf einen quadratischen Zusammenhang hindeutet."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_2" hidden="1">"Unabhängig: Monat; Abhängig: Aktienpreis | Zusammenhang: Monat → Aktienpreis | Diagramm: Punkt- und Liniendiagramm; Tren"&amp;"dlinie: kein | Messpunkte: 6 von 6; Mittelwert y: 135.1 | Statistik: Median y: 145; Min–Max y: 90–170; Stdabw. y: 32.63;"&amp;" Korrelation: 0.4063 | Veränderung: Kurs 100.4 → 160; absolut +59.6; Prozent: +59.36% | KI-Einschätzung: 90% — Monat ist"&amp;" unabhängige Zeitvariable, Aktienpreis abhängige Messgröße. Verlauf stark volatil mit Abfall im 4. Monat, keine Trendfun"&amp;"ktion st..."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_3" hidden="1">"Unabhängig: Strecke [m]; Abhängig: Zeit [s] | Zusammenhang: Strecke in m → Zeit in s | Diagramm: Säulendiagramm; Trendli"&amp;"nie: gleitender Durchschnitt (Periode 2) | Messpunkte: 7 von 7; Mittelwert y: 4 s | Statistik: Median y: 4 s; Min–Max y:"&amp;" 1–7 s; Stdabw. y: 2.16 s; Korrelation: 0.9774 | KI-Einschätzung: 100% — Strecke ist quadratisch abhängig von Zeit (Stre"&amp;"cke = Zeit²), perfekte quadratische Korrelation (R²=1.0)."</definedName>
     <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_4" hidden="1">"Unabhängig: Strecke [m]; Abhängig: Zeit [s] | Zusammenhang: Strecke in m → Zeit in s | Diagramm: Punktdiagramm (XY); Tre"&amp;"ndlinie: polynomisch (Grad 2) | Messpunkte: 7 von 7; Mittelwert y: 4 s | Statistik: Median y: 4 s; Min–Max y: 1–7 s; Std"&amp;"abw. y: 2.16 s; Korrelation: 0.9774 | KI-Einschätzung: 100% — The data represents a perfect quadratic relationship where"&amp;" distance (Strecke in m) is the square of time (Zeit in s), with R² = 1.0 for a..."</definedName>
-    <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_5" hidden="1">"Unabhängig: Zeit [s]; Abhängig: Masse [kg] | Zusammenhang: Zeit in s → Masse in kg | Diagramm: Säulendiagramm; Trendlini"&amp;"e: exponentiell | Messpunkte: 7 von 7; Mittelwert y: 18.14 kg | Statistik: Median y: 8 kg; Min–Max y: 1–64 kg; Stdabw. y"&amp;": 22.94 kg; Korrelation: 0.8779 | KI-Einschätzung: 95% — Exponential fit (R²=1) shows mass doubling each second, best mo"&amp;"del is exponential."</definedName>
+    <definedName name="_PLVS_ULTRA_Analysis_PLVS_ULTRA_Chart_5" hidden="1">"Unabhängig: Zeit [s]; Abhängig: Masse [kg] | Zusammenhang: Zeit in s → Masse in kg | Diagramm: Punktdiagramm (XY); Trend"&amp;"linie: exponentiell | Messpunkte: 7 von 7; Mittelwert y: 18.14 kg | Statistik: Median y: 8 kg; Min–Max y: 1–64 kg; Stdab"&amp;"w. y: 22.94 kg; Korrelation: 0.8779 | KI-Einschätzung: 95% — Exponential fit (R²=1) shows mass doubling each second, bes"&amp;"t model is exponential."</definedName>
     <definedName name="_PLVS_ULTRA_ChartSheet" hidden="1">"Tabelle1"</definedName>
     <definedName name="_PLVS_ULTRA_LastChart" hidden="1">"PLVS_ULTRA_Chart_5"</definedName>
     <definedName name="_PLVS_ULTRA_SourceAddress" hidden="1">"$D$1:$E$8"</definedName>
@@ -29,7 +29,7 @@
     <definedName name="_PLVS_ULTRA_SourceSheet" hidden="1">"Tabelle1"</definedName>
     <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_3" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$A$1:$B$8"",""spec"":{""x_column"":""Strecke in m"",""y_column"":""Zeit in s"",""x_label"":""Strecke [m"&amp;"]"",""y_label"":""Zeit [s]"",""x_unit"":""m"",""y_unit"":""s"",""chart_type"":""column"",""x_min"":null,""x_max"":null,""y_min"":null,""y_max"":n"&amp;"ull,""origin"":false,""trendline"":""moving_average"",""polynomial_degree"":2,""moving_average_period"":2,""x_error_column"":null,""y"&amp;"_error_column"":null,""independent_variable"":""Strecke in m"",""dependent_variable"":""Zeit in s"",""show_points"":false,""connect_"&amp;"points"":false,""confidence"":1.0,""reason"":""Strecke ist quadratisch abhängig von Zeit (Strecke = Zeit²), perfekte quadratis"&amp;"che Korrelation (R²=1.0).""},""settings"":{""show_points"":false,""connect_points"":false,""legend"":true,""title"":""Zeit [s] in Ab"&amp;"hängigkeit von Strecke [m]"",""line_width"":3.0,""point_size"":5,""series_color"":3243501,""text_formats"":{""title"":{""name"":""Time"&amp;"s New Roman""},""x_axis"":{""name"":""Times New Roman"",""size"":20,""italic"":true}},""text_target"":""x_axis""}}"</definedName>
     <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_4" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$A$1:$B$8"",""spec"":{""x_column"":""Strecke in m"",""y_column"":""Zeit in s"",""x_label"":""Strecke [m"&amp;"]"",""y_label"":""Zeit [s]"",""x_unit"":""m"",""y_unit"":""s"",""chart_type"":""scatter"",""x_min"":null,""x_max"":null,""y_min"":null,""y_max"":"&amp;"null,""origin"":false,""trendline"":""polynomial"",""polynomial_degree"":2,""moving_average_period"":3,""x_error_column"":null,""y_er"&amp;"ror_column"":null,""independent_variable"":""Strecke in m"",""dependent_variable"":""Zeit in s"",""show_points"":true,""connect_poin"&amp;"ts"":false,""confidence"":1.0,""reason"":""The data represents a perfect quadratic relationship where distance (Strecke in m) "&amp;"is the square of time (Zeit in s), with R² = 1.0 for a quadratic fit.""},""settings"":{""show_points"":true,""connect_points"":"&amp;"false,""legend"":false,""title"":""Zeit [s] in Abhängigkeit von Strecke [m]"",""line_width"":3.0,""point_size"":5,""text_formats"":{"&amp;"""title"":{""italic"":true,""size"":12,""name"":""Times New Roman""},""x_axis"":{""italic"":true,""size"":20},""y_axis"":{""italic"":true,""n"&amp;"ame"":""Times New Roman""}},""text_target"":""title"",""series_color"":3243501,""line_color"":8544277,""gridlines_enabled"":true}}"</definedName>
-    <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_5" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$D$1:$E$8"",""spec"":{""x_column"":""Zeit in s"",""y_column"":""Masse in kg"",""x_label"":""Zeit [s]"","""&amp;"y_label"":""Masse [kg]"",""x_unit"":""s"",""y_unit"":""kg"",""chart_type"":""column"",""x_min"":1.0,""x_max"":7.0,""y_min"":1.0,""y_max"":64.0,"&amp;"""origin"":false,""trendline"":""exponential"",""polynomial_degree"":2,""moving_average_period"":3,""x_error_column"":null,""y_error_"&amp;"column"":null,""independent_variable"":""Zeit in s"",""dependent_variable"":""Masse in kg"",""show_points"":false,""connect_points"":"&amp;"false,""confidence"":0.95,""reason"":""Exponential fit (R²=1) shows mass doubling each second, best model is exponential.""},"""&amp;"settings"":{""show_points"":false,""connect_points"":false,""legend"":false,""gridlines_enabled"":true,""title"":""Masse [kg] in Abh"&amp;"ängigkeit von Zeit [s]"",""text_formats"":{""title"":{""name"":""Segoe UI""}},""point_size"":5,""line_color"":16777215,""line_width"":3"&amp;".0,""series_color"":12874308}}"</definedName>
+    <definedName name="_PLVS_ULTRA_State_PLVS_ULTRA_Chart_5" hidden="1">"{""sheet"":""Tabelle1"",""address"":""$D$1:$E$8"",""spec"":{""x_column"":""Zeit in s"",""y_column"":""Masse in kg"",""x_label"":""Zeit [s]"","""&amp;"y_label"":""Masse [kg]"",""x_unit"":""s"",""y_unit"":""kg"",""chart_type"":""scatter"",""x_min"":1.0,""x_max"":7.0,""y_min"":1.0,""y_max"":64.0"&amp;",""origin"":false,""trendline"":""exponential"",""polynomial_degree"":2,""moving_average_period"":3,""x_error_column"":null,""y_error"&amp;"_column"":null,""independent_variable"":""Zeit in s"",""dependent_variable"":""Masse in kg"",""show_points"":true,""connect_points"":"&amp;"false,""confidence"":0.95,""reason"":""Exponential fit (R²=1) shows mass doubling each second, best model is exponential.""},"""&amp;"settings"":{""show_points"":true,""connect_points"":false,""legend"":false,""gridlines_enabled"":true,""title"":""Masse [kg] in Abhä"&amp;"ngigkeit von Zeit [s]"",""text_formats"":{""title"":{""name"":""Segoe UI""}},""point_size"":5,""line_color"":16777215,""line_width"":3."&amp;"0,""series_color"":12874308}}"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -163,9 +163,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -177,10 +176,8 @@
             <a:solidFill>
               <a:srgbClr val="4472C4"/>
             </a:solidFill>
-            <a:ln w="38100" cap="rnd" cmpd="sng" algn="ctr">
+            <a:ln w="38100">
               <a:noFill/>
-              <a:prstDash val="solid"/>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
             <a:extLst>
@@ -195,14 +192,28 @@
               </a:ext>
             </a:extLst>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
           <c:trendline>
             <c:name>Exponential Fit</c:name>
             <c:trendlineType val="exp"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
-          <c:cat>
+          <c:xVal>
             <c:numRef>
               <c:f>Tabelle1!$E$2:$E$8</c:f>
               <c:numCache>
@@ -231,8 +242,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Tabelle1!$D$2:$D$8</c:f>
               <c:numCache>
@@ -261,7 +272,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-4230-4937-A3A2-91154FC9F654}"/>
@@ -276,11 +288,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
         <c:axId val="1231230416"/>
         <c:axId val="1231236656"/>
-      </c:barChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="1231230416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -312,11 +323,8 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1231236656"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="1231236656"/>
         <c:scaling>
@@ -326,6 +334,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines/>
         <c:title>
           <c:tx>
             <c:rich>
@@ -350,7 +359,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1231230416"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -376,16 +385,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>596557</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>68648</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>347705</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25742</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>86841</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>15445</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>601705</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>152742</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
